--- a/teacher_forms/014_student_questionnaire--teacher_forms.xlsx
+++ b/teacher_forms/014_student_questionnaire--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Student Satisfaction</t>
+          <t>Student Satisfaction2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -913,7 +913,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Class Time</t>
+          <t>Class Day</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -954,12 +954,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>class_time</t>
+          <t>class_time_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Class Time</t>
+          <t>Class Time 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Class Time</t>
+          <t>Class Time2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high',_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High', 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium',_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium', 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low',_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low', 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'very_low',_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Very Low', 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high',_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High', 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium',_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium', 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low',_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low', 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'very_low',_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Very Low', 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
